--- a/AAII_Financials/Yearly/CVCO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CVCO_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/CVCO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CVCO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>CVCO</t>
   </si>
@@ -656,198 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45017</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44653</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44289</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43918</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43554</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42826</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42462</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42091</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41727</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41363</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1794800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2142700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1627200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1108100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1061800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>962700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>871200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>773800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>712400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>566700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>533300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>452300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>443100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1367900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1587800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1218400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>869100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>831300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>757000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>690600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>615800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>567900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>440500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>413900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>351900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>347100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>426900</v>
+      </c>
+      <c r="E10" s="3">
         <v>554900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>408700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>239000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>230500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>205700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>180700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>158000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>144400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>126100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>119500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>95900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,9 +919,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,9 +964,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -962,14 +982,14 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>2900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2100</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -980,18 +1000,21 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-22000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1031,9 +1054,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1047,92 +1073,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1615800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1846100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1424700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1019200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>976900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>878600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>797500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>717000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>666000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>528200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>501800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>431300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>404900</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E18" s="3">
         <v>296600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>202500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>88800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>84900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>84100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>73800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>56800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>46300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>38500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>31500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>38200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1149,112 +1182,119 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E20" s="3">
         <v>11100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1300</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>219400</v>
+      </c>
+      <c r="E21" s="3">
         <v>324600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>223700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>104000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>100300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>94800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>86900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>63400</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>45700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>36700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>45000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="3">
         <v>900</v>
-      </c>
-      <c r="E22" s="3">
-        <v>700</v>
       </c>
       <c r="F22" s="3">
         <v>700</v>
       </c>
       <c r="G22" s="3">
+        <v>700</v>
+      </c>
+      <c r="H22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>4400</v>
       </c>
       <c r="J22" s="3">
         <v>4400</v>
@@ -1263,104 +1303,113 @@
         <v>4400</v>
       </c>
       <c r="L22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="M22" s="3">
         <v>4600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7300</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>199200</v>
+      </c>
+      <c r="E23" s="3">
         <v>306800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>212000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>96900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>93000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>86700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>78500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>55300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>44000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>37300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>27800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>32200</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E24" s="3">
         <v>65900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>20300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>17900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>17700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1400,93 +1449,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>157900</v>
+      </c>
+      <c r="E26" s="3">
         <v>240800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>197700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>76600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>75100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>68900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>56700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>38000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>28500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>23800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>29700</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>157800</v>
+      </c>
+      <c r="E27" s="3">
         <v>240600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>197700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>76600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>75100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>68900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>56700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>38000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>23800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>15200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1526,9 +1584,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1541,17 +1602,17 @@
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>4800</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1568,9 +1629,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1610,9 +1674,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1652,93 +1719,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1300</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>157800</v>
+      </c>
+      <c r="E33" s="3">
         <v>240600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>197700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>76600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>75100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>68600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>61500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>38000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>28500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>23800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>15200</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1778,98 +1854,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>157800</v>
+      </c>
+      <c r="E35" s="3">
         <v>240600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>197700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>76600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>75100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>68600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>61500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>38000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>28500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>23800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>15200</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45017</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44653</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44289</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43918</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43554</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42826</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42462</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42091</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41727</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41363</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1886,8 +1971,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1904,386 +1990,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>352700</v>
+      </c>
+      <c r="E41" s="3">
         <v>271400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>244200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>322300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>241800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>187400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>186800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>132500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>96600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>72900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>47800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41100</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E42" s="3">
         <v>15000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>20100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5400</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E43" s="3">
         <v>150400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>149300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>104300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>90600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>86000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>71600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>70300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>54600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>53400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>43600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>42900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>37600</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>241300</v>
+      </c>
+      <c r="E44" s="3">
         <v>263100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>244000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>131200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>113500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>116200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>109200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>93900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>94800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>75300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>69700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>68800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>62200</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>98400</v>
+      </c>
+      <c r="E45" s="3">
         <v>104600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>86600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>74500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>55600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>59900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>39200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>41400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>24700</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>851800</v>
+      </c>
+      <c r="E46" s="3">
         <v>804600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>744100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>651800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>516200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>462000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>418600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>356800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>298700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>265500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>227800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>194400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>171000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E47" s="3">
         <v>103700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>100100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>97200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>112600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>116600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>108500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>112800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>118600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>114600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>113900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>120500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>130100</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>263200</v>
+      </c>
+      <c r="E48" s="3">
         <v>255000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>181000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>113000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>91100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>63500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>63400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>57000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>55100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>48200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>46200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50100</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>150200</v>
+      </c>
+      <c r="E49" s="3">
         <v>144300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>129500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>89500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>90200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>82700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>83000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>80000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>80400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>76700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>78100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>79400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>80900</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2323,9 +2437,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2365,14 +2482,17 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
@@ -2384,32 +2504,35 @@
         <v>300</v>
       </c>
       <c r="H52" s="3">
+        <v>300</v>
+      </c>
+      <c r="I52" s="3">
         <v>400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>700</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1100</v>
       </c>
       <c r="L52" s="3">
         <v>1100</v>
       </c>
       <c r="M52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N52" s="3">
         <v>1200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5200</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2449,51 +2572,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1354200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1308000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1155000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>951800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>810400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>725200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>674800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>607300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>553800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>502600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>469200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>444500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>437300</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2510,8 +2639,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2528,176 +2658,189 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E57" s="3">
         <v>30700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11700</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>300</v>
+      </c>
+      <c r="E58" s="3">
         <v>3100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>27200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6600</v>
-      </c>
-      <c r="M58" s="3">
-        <v>10200</v>
       </c>
       <c r="N58" s="3">
         <v>10200</v>
       </c>
       <c r="O58" s="3">
+        <v>10200</v>
+      </c>
+      <c r="P58" s="3">
         <v>15300</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>239400</v>
+      </c>
+      <c r="E59" s="3">
         <v>259600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>250300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>203100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>139900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>124100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>125300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>109800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>97900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>77100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>73500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>62700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>58500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>273300</v>
+      </c>
+      <c r="E60" s="3">
         <v>293400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>294200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>237100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>172100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>174000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>176300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>140200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>125100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>101500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>99000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>87000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>85500</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2705,83 +2848,89 @@
         <v>7800</v>
       </c>
       <c r="E61" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F61" s="3">
         <v>10800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>33800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>54900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>60400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>59900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>72100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>80700</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E62" s="3">
         <v>29300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>21100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>20600</v>
       </c>
       <c r="L62" s="3">
         <v>20600</v>
       </c>
       <c r="M62" s="3">
+        <v>20600</v>
+      </c>
+      <c r="N62" s="3">
         <v>19900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16200</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2821,9 +2970,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2863,9 +3015,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2905,51 +3060,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>320700</v>
+      </c>
+      <c r="E66" s="3">
         <v>331700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>324500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>268200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>202800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>195600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>217700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>212900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>200600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>182400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>178800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>267600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>269000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2966,8 +3127,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3007,9 +3169,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3049,9 +3214,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3091,9 +3259,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3133,51 +3304,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1027100</v>
+      </c>
+      <c r="E72" s="3">
         <v>869300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>628800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>431100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>355100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>280100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>209400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>148100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>110200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>81600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>57800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>41600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>36600</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3217,9 +3394,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3259,9 +3439,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3301,51 +3484,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1033400</v>
+      </c>
+      <c r="E76" s="3">
         <v>976300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>830500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>683600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>607600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>529600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>457100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>394400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>353200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>320200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>290400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>176900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>168300</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3385,98 +3574,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45017</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44653</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44289</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43918</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43554</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42826</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42462</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42091</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41727</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41363</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>157800</v>
+      </c>
+      <c r="E81" s="3">
         <v>240600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>197700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>76600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>75100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>68600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>61500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>38000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>28500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>23800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>15200</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3493,50 +3691,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E83" s="3">
         <v>16900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3700</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3800</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5600</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3576,9 +3778,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3618,9 +3823,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3660,9 +3868,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3702,9 +3913,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3744,51 +3958,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>224700</v>
+      </c>
+      <c r="E89" s="3">
         <v>255700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>144200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>114000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>101700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>32800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>59000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>45800</v>
-      </c>
-      <c r="K89" s="3">
-        <v>25700</v>
       </c>
       <c r="L89" s="3">
         <v>25700</v>
       </c>
       <c r="M89" s="3">
-        <v>20700</v>
+        <v>25700</v>
       </c>
       <c r="N89" s="3">
         <v>20700</v>
       </c>
       <c r="O89" s="3">
+        <v>20700</v>
+      </c>
+      <c r="P89" s="3">
         <v>16400</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3805,50 +4025,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-44100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-2200</v>
       </c>
       <c r="L91" s="3">
         <v>-2200</v>
       </c>
       <c r="M91" s="3">
-        <v>-800</v>
+        <v>-2200</v>
       </c>
       <c r="N91" s="3">
         <v>-800</v>
       </c>
       <c r="O91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P91" s="3">
         <v>-70100</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3888,9 +4112,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3930,51 +4157,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-129300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-159100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7100</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2100</v>
       </c>
-      <c r="M94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23100</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3991,8 +4224,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4032,9 +4266,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4074,9 +4311,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4116,9 +4356,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4158,51 +4401,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-107700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-102200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-65100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-20800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-26400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3000</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-28800</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4227,64 +4476,70 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>85300</v>
+      </c>
+      <c r="E102" s="3">
         <v>24200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-80000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>83700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>55700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>54400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>35800</v>
-      </c>
-      <c r="K102" s="3">
-        <v>23600</v>
       </c>
       <c r="L102" s="3">
         <v>23600</v>
       </c>
       <c r="M102" s="3">
-        <v>6700</v>
+        <v>23600</v>
       </c>
       <c r="N102" s="3">
         <v>6700</v>
       </c>
       <c r="O102" s="3">
+        <v>6700</v>
+      </c>
+      <c r="P102" s="3">
         <v>-35400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CVCO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CVCO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>CVCO</t>
   </si>
@@ -775,10 +775,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1367900</v>
+        <v>1317700</v>
       </c>
       <c r="E9" s="3">
-        <v>1587800</v>
+        <v>1545900</v>
       </c>
       <c r="F9" s="3">
         <v>1218400</v>
@@ -820,25 +820,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>426900</v>
+        <v>403600</v>
       </c>
       <c r="E10" s="3">
-        <v>554900</v>
+        <v>533600</v>
       </c>
       <c r="F10" s="3">
-        <v>408700</v>
+        <v>408000</v>
       </c>
       <c r="G10" s="3">
-        <v>239000</v>
+        <v>238200</v>
       </c>
       <c r="H10" s="3">
-        <v>230500</v>
+        <v>229000</v>
       </c>
       <c r="I10" s="3">
-        <v>205700</v>
+        <v>202300</v>
       </c>
       <c r="J10" s="3">
-        <v>180700</v>
+        <v>176300</v>
       </c>
       <c r="K10" s="3">
         <v>158000</v>
@@ -973,26 +973,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-8400</v>
       </c>
       <c r="H14" s="3">
-        <v>2900</v>
+        <v>-1100</v>
       </c>
       <c r="I14" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+        <v>300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-5800</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1019,25 +1019,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>18500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,25 +1080,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1615800</v>
+        <v>1617500</v>
       </c>
       <c r="E17" s="3">
-        <v>1846100</v>
+        <v>1844600</v>
       </c>
       <c r="F17" s="3">
-        <v>1424700</v>
+        <v>1425400</v>
       </c>
       <c r="G17" s="3">
-        <v>1019200</v>
+        <v>1020000</v>
       </c>
       <c r="H17" s="3">
-        <v>976900</v>
+        <v>978400</v>
       </c>
       <c r="I17" s="3">
-        <v>878600</v>
+        <v>882100</v>
       </c>
       <c r="J17" s="3">
-        <v>797500</v>
+        <v>801900</v>
       </c>
       <c r="K17" s="3">
         <v>717000</v>
@@ -1125,25 +1125,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>179000</v>
+        <v>177300</v>
       </c>
       <c r="E18" s="3">
-        <v>296600</v>
+        <v>298100</v>
       </c>
       <c r="F18" s="3">
-        <v>202500</v>
+        <v>201800</v>
       </c>
       <c r="G18" s="3">
-        <v>88800</v>
+        <v>88100</v>
       </c>
       <c r="H18" s="3">
-        <v>84900</v>
+        <v>83400</v>
       </c>
       <c r="I18" s="3">
-        <v>84100</v>
+        <v>80700</v>
       </c>
       <c r="J18" s="3">
-        <v>73800</v>
+        <v>69400</v>
       </c>
       <c r="K18" s="3">
         <v>56800</v>
@@ -1189,25 +1189,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>21800</v>
+        <v>900</v>
       </c>
       <c r="E20" s="3">
-        <v>11100</v>
+        <v>500</v>
       </c>
       <c r="F20" s="3">
-        <v>10200</v>
+        <v>-1000</v>
       </c>
       <c r="G20" s="3">
-        <v>8800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>9600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>9100</v>
+        <v>1700</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>2900</v>
@@ -1234,25 +1234,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>219400</v>
+        <v>195000</v>
       </c>
       <c r="E21" s="3">
-        <v>324600</v>
+        <v>314500</v>
       </c>
       <c r="F21" s="3">
-        <v>223700</v>
+        <v>213800</v>
       </c>
       <c r="G21" s="3">
-        <v>104000</v>
+        <v>92700</v>
       </c>
       <c r="H21" s="3">
-        <v>100300</v>
+        <v>89200</v>
       </c>
       <c r="I21" s="3">
-        <v>94800</v>
+        <v>85400</v>
       </c>
       <c r="J21" s="3">
-        <v>86900</v>
+        <v>73400</v>
       </c>
       <c r="K21" s="3">
         <v>63400</v>
@@ -1278,26 +1278,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>1600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>4400</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>4400</v>
@@ -1384,10 +1384,10 @@
         <v>17900</v>
       </c>
       <c r="I24" s="3">
-        <v>17700</v>
+        <v>18100</v>
       </c>
       <c r="J24" s="3">
-        <v>21800</v>
+        <v>17000</v>
       </c>
       <c r="K24" s="3">
         <v>17300</v>
@@ -1474,10 +1474,10 @@
         <v>75100</v>
       </c>
       <c r="I26" s="3">
-        <v>68900</v>
+        <v>68600</v>
       </c>
       <c r="J26" s="3">
-        <v>56700</v>
+        <v>61500</v>
       </c>
       <c r="K26" s="3">
         <v>38000</v>
@@ -1513,16 +1513,16 @@
         <v>197700</v>
       </c>
       <c r="G27" s="3">
-        <v>76600</v>
+        <v>76700</v>
       </c>
       <c r="H27" s="3">
         <v>75100</v>
       </c>
       <c r="I27" s="3">
-        <v>68900</v>
+        <v>68600</v>
       </c>
       <c r="J27" s="3">
-        <v>56700</v>
+        <v>61500</v>
       </c>
       <c r="K27" s="3">
         <v>38000</v>
@@ -1593,26 +1593,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1729,25 +1729,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-21800</v>
+        <v>-900</v>
       </c>
       <c r="E32" s="3">
-        <v>-11100</v>
+        <v>-500</v>
       </c>
       <c r="F32" s="3">
-        <v>-10200</v>
+        <v>1000</v>
       </c>
       <c r="G32" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-9100</v>
+        <v>-1700</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>-2900</v>
@@ -2087,25 +2087,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>141200</v>
+        <v>77100</v>
       </c>
       <c r="E43" s="3">
-        <v>150400</v>
+        <v>89300</v>
       </c>
       <c r="F43" s="3">
-        <v>149300</v>
+        <v>96100</v>
       </c>
       <c r="G43" s="3">
-        <v>104300</v>
+        <v>47400</v>
       </c>
       <c r="H43" s="3">
-        <v>90600</v>
+        <v>42800</v>
       </c>
       <c r="I43" s="3">
-        <v>86000</v>
+        <v>40700</v>
       </c>
       <c r="J43" s="3">
-        <v>71600</v>
+        <v>35000</v>
       </c>
       <c r="K43" s="3">
         <v>70300</v>
@@ -2135,7 +2135,7 @@
         <v>241300</v>
       </c>
       <c r="E44" s="3">
-        <v>263100</v>
+        <v>263200</v>
       </c>
       <c r="F44" s="3">
         <v>244000</v>
@@ -2177,25 +2177,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>98400</v>
+        <v>3900</v>
       </c>
       <c r="E45" s="3">
-        <v>104600</v>
+        <v>2900</v>
       </c>
       <c r="F45" s="3">
-        <v>86600</v>
+        <v>2200</v>
       </c>
       <c r="G45" s="3">
-        <v>74500</v>
+        <v>1400</v>
       </c>
       <c r="H45" s="3">
-        <v>55600</v>
+        <v>1500</v>
       </c>
       <c r="I45" s="3">
-        <v>59900</v>
+        <v>4600</v>
       </c>
       <c r="J45" s="3">
-        <v>39200</v>
+        <v>1500</v>
       </c>
       <c r="K45" s="3">
         <v>48800</v>
@@ -2267,25 +2267,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>88400</v>
+        <v>17300</v>
       </c>
       <c r="E47" s="3">
-        <v>103700</v>
+        <v>18600</v>
       </c>
       <c r="F47" s="3">
-        <v>100100</v>
+        <v>34900</v>
       </c>
       <c r="G47" s="3">
-        <v>97200</v>
+        <v>35000</v>
       </c>
       <c r="H47" s="3">
-        <v>112600</v>
+        <v>31600</v>
       </c>
       <c r="I47" s="3">
-        <v>116600</v>
+        <v>32100</v>
       </c>
       <c r="J47" s="3">
-        <v>108500</v>
+        <v>33600</v>
       </c>
       <c r="K47" s="3">
         <v>112800</v>
@@ -2710,13 +2710,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>5600</v>
       </c>
       <c r="E58" s="3">
-        <v>3100</v>
+        <v>7100</v>
       </c>
       <c r="F58" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>1900</v>
@@ -2755,25 +2755,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>239400</v>
+        <v>160700</v>
       </c>
       <c r="E59" s="3">
-        <v>259600</v>
+        <v>174200</v>
       </c>
       <c r="F59" s="3">
-        <v>250300</v>
+        <v>178300</v>
       </c>
       <c r="G59" s="3">
-        <v>203100</v>
+        <v>153300</v>
       </c>
       <c r="H59" s="3">
-        <v>139900</v>
+        <v>104200</v>
       </c>
       <c r="I59" s="3">
-        <v>124100</v>
+        <v>83300</v>
       </c>
       <c r="J59" s="3">
-        <v>125300</v>
+        <v>72000</v>
       </c>
       <c r="K59" s="3">
         <v>109800</v>
@@ -2845,19 +2845,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7800</v>
+        <v>42900</v>
       </c>
       <c r="E61" s="3">
-        <v>7800</v>
+        <v>29500</v>
       </c>
       <c r="F61" s="3">
-        <v>10800</v>
+        <v>24000</v>
       </c>
       <c r="G61" s="3">
-        <v>10300</v>
+        <v>23700</v>
       </c>
       <c r="H61" s="3">
-        <v>12700</v>
+        <v>23400</v>
       </c>
       <c r="I61" s="3">
         <v>14600</v>
@@ -2889,26 +2889,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>39700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>29300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>18700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>20800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>18000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>7000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>7600</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>21100</v>
@@ -3073,10 +3073,10 @@
         <v>320700</v>
       </c>
       <c r="E66" s="3">
-        <v>331700</v>
+        <v>330500</v>
       </c>
       <c r="F66" s="3">
-        <v>324500</v>
+        <v>323700</v>
       </c>
       <c r="G66" s="3">
         <v>268200</v>
@@ -3698,25 +3698,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>18500</v>
+        <v>17000</v>
       </c>
       <c r="E83" s="3">
-        <v>16900</v>
+        <v>14800</v>
       </c>
       <c r="F83" s="3">
-        <v>11000</v>
+        <v>9600</v>
       </c>
       <c r="G83" s="3">
-        <v>6300</v>
+        <v>5600</v>
       </c>
       <c r="H83" s="3">
-        <v>5800</v>
+        <v>5200</v>
       </c>
       <c r="I83" s="3">
-        <v>4700</v>
+        <v>4400</v>
       </c>
       <c r="J83" s="3">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="K83" s="3">
         <v>3700</v>
@@ -4455,26 +4455,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/CVCO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CVCO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>CVCO</t>
   </si>
@@ -656,211 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45017</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44653</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44289</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43918</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43554</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42826</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42462</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42091</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41727</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41363</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2015500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1794800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2142700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1627200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1108100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1061800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>962700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>871200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>773800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>712400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>566700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>533300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>452300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>443100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1491300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1317700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1545900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1218400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>869100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>831300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>757000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>690600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>615800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>567900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>440500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>413900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>351900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>347100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>403600</v>
+        <v>443300</v>
       </c>
       <c r="E10" s="3">
-        <v>533600</v>
+        <v>405200</v>
       </c>
       <c r="F10" s="3">
+        <v>533900</v>
+      </c>
+      <c r="G10" s="3">
         <v>408000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>238200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>229000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>202300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>176300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>158000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>144400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>126100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>119500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>100400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>95900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +890,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,9 +935,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,81 +983,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-5700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-8400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E15" s="3">
         <v>18500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1057,9 +1079,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1074,98 +1099,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1617500</v>
+        <v>1815200</v>
       </c>
       <c r="E17" s="3">
-        <v>1844600</v>
+        <v>1615800</v>
       </c>
       <c r="F17" s="3">
+        <v>1844300</v>
+      </c>
+      <c r="G17" s="3">
         <v>1425400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1020000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>978400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>882100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>801900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>717000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>666000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>528200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>501800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>431300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>404900</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>177300</v>
+        <v>200300</v>
       </c>
       <c r="E18" s="3">
-        <v>298100</v>
+        <v>179000</v>
       </c>
       <c r="F18" s="3">
+        <v>298400</v>
+      </c>
+      <c r="G18" s="3">
         <v>201800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>88100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>83400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>80700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>69400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>56800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>38500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>31500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>38200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1183,109 +1215,116 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1300</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>195000</v>
+        <v>220800</v>
       </c>
       <c r="E21" s="3">
-        <v>314500</v>
+        <v>196600</v>
       </c>
       <c r="F21" s="3">
+        <v>314800</v>
+      </c>
+      <c r="G21" s="3">
         <v>213800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>92700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>89200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>85400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>73400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>63400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>45700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>36700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>26600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>45000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F22" s="3">
+        <v>300</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>8</v>
@@ -1299,117 +1338,126 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>4400</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>4400</v>
       </c>
       <c r="M22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="N22" s="3">
         <v>4600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7300</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>211100</v>
+      </c>
+      <c r="E23" s="3">
         <v>199200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>306800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>212000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>96900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>93000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>86700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>78500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>55300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>44000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>37300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>27800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>16600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>32200</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E24" s="3">
         <v>41300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>65900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>20300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>17900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>18100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>13500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2500</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1452,99 +1500,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E26" s="3">
         <v>157900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>240800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>197700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>76600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>75100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>68600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>61500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>38000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>28500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>29700</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E27" s="3">
         <v>157800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>240600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>197700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>76700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>75100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>68600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>61500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>38000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>28500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>15200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1587,9 +1644,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1674,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1632,9 +1692,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1677,9 +1740,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1722,99 +1788,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E33" s="3">
         <v>157800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>240600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>197700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>76600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>75100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>68600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>61500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>38000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>28500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>15200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1857,104 +1932,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E35" s="3">
         <v>157800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>240600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>197700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>76600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>75100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>68600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>61500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>38000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>28500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>15200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45017</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44653</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44289</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43918</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43554</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42826</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42462</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42091</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41727</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41363</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1972,8 +2056,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1991,323 +2076,345 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>356200</v>
+      </c>
+      <c r="E41" s="3">
         <v>352700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>271400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>244200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>322300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>241800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>187400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>186800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>132500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>97800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>96600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>72900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>41100</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E42" s="3">
         <v>18300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>20100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>14600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5400</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>105800</v>
+      </c>
+      <c r="E43" s="3">
         <v>77100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>89300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>96100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>47400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>42800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>35000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>70300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>54600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>53400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>43600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>42900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>37600</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>252700</v>
+      </c>
+      <c r="E44" s="3">
         <v>241300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>263200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>244000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>131200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>113500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>116200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>109200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>93900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>94800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>75300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>69700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>68800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>62200</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>41400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24700</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>910200</v>
+      </c>
+      <c r="E46" s="3">
         <v>851800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>804600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>744100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>651800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>516200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>462000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>418600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>356800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>298700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>265500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>227800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>194400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>171000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E47" s="3">
         <v>17300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>18600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>34900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>35000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>31600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>32100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>33600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>112800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>118600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>114600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>113900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>120500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>130100</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2315,89 +2422,95 @@
         <v>263200</v>
       </c>
       <c r="E48" s="3">
+        <v>263200</v>
+      </c>
+      <c r="F48" s="3">
         <v>255000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>181000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>113000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>91100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>63500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>63400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>55100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>48200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>46200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>50100</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>138700</v>
+      </c>
+      <c r="E49" s="3">
         <v>150200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>144300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>129500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>89500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>90200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>82700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>83000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>80000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>80400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>76700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>78100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>79400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>80900</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2440,9 +2553,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2485,9 +2601,12 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2495,7 +2614,7 @@
         <v>600</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
@@ -2507,32 +2626,35 @@
         <v>300</v>
       </c>
       <c r="I52" s="3">
+        <v>300</v>
+      </c>
+      <c r="J52" s="3">
         <v>400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>700</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1100</v>
       </c>
       <c r="M52" s="3">
         <v>1100</v>
       </c>
       <c r="N52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O52" s="3">
         <v>1200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5200</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2575,54 +2697,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1406600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1354200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1308000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1155000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>951800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>810400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>725200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>674800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>607300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>553800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>502600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>469200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>444500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>437300</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2640,8 +2768,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2659,233 +2788,249 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E57" s="3">
         <v>33500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>43100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E58" s="3">
         <v>5600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7100</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>27200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6600</v>
-      </c>
-      <c r="N58" s="3">
-        <v>10200</v>
       </c>
       <c r="O58" s="3">
         <v>10200</v>
       </c>
       <c r="P58" s="3">
+        <v>10200</v>
+      </c>
+      <c r="Q58" s="3">
         <v>15300</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>179800</v>
+      </c>
+      <c r="E59" s="3">
         <v>160700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>174200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>178300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>153300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>104200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>83300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>72000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>109800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>97900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>77100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>73500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>62700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>58500</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>303200</v>
+      </c>
+      <c r="E60" s="3">
         <v>273300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>293400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>294200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>237100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>172100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>174000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>176300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>140200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>125100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>101500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>99000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>87000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>85500</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E61" s="3">
         <v>42900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>33800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>54900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>60400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>59900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>72100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>80700</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2910,27 +3055,30 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>21100</v>
-      </c>
-      <c r="L62" s="3">
-        <v>20600</v>
       </c>
       <c r="M62" s="3">
         <v>20600</v>
       </c>
       <c r="N62" s="3">
+        <v>20600</v>
+      </c>
+      <c r="O62" s="3">
         <v>19900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16200</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2973,9 +3121,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3018,9 +3169,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3063,54 +3217,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>342100</v>
+      </c>
+      <c r="E66" s="3">
         <v>320700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>330500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>323700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>268200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>202800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>195600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>217700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>212900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>200600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>182400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>178800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>267600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>269000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3128,8 +3288,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3172,9 +3333,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3217,9 +3381,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3262,9 +3429,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3307,54 +3477,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1198200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1027100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>869300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>628800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>431100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>355100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>280100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>209400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>148100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>110200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>81600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>57800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>41600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>36600</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3397,9 +3573,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3442,9 +3621,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3487,54 +3669,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1064600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1033400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>976300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>830500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>683600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>607600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>529600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>457100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>394400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>353200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>320200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>290400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>176900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>168300</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3577,104 +3765,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45017</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44653</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44289</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43918</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43554</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42826</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42462</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42091</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41727</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41363</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E81" s="3">
         <v>157800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>240600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>197700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>76600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>75100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>68600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>61500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>38000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>28500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>15200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3692,53 +3889,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E83" s="3">
         <v>17000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3700</v>
       </c>
       <c r="K83" s="3">
         <v>3700</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="L83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>3800</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>4000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5600</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3781,9 +3982,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3826,9 +4030,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3871,9 +4078,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3916,9 +4126,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3961,54 +4174,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>178500</v>
+      </c>
+      <c r="E89" s="3">
         <v>224700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>255700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>144200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>114000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>101700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>32800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>59000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>45800</v>
-      </c>
-      <c r="L89" s="3">
-        <v>25700</v>
       </c>
       <c r="M89" s="3">
         <v>25700</v>
       </c>
       <c r="N89" s="3">
-        <v>20700</v>
+        <v>25700</v>
       </c>
       <c r="O89" s="3">
         <v>20700</v>
       </c>
       <c r="P89" s="3">
+        <v>20700</v>
+      </c>
+      <c r="Q89" s="3">
         <v>16400</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4026,53 +4245,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-44100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-25500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-2200</v>
       </c>
       <c r="M91" s="3">
         <v>-2200</v>
       </c>
       <c r="N91" s="3">
-        <v>-800</v>
+        <v>-2200</v>
       </c>
       <c r="O91" s="3">
         <v>-800</v>
       </c>
       <c r="P91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-70100</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4115,9 +4338,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4160,54 +4386,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-129300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-159100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7100</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>-2100</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-2100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4225,8 +4457,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4269,9 +4502,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4314,9 +4550,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4359,9 +4598,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4404,54 +4646,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-147900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-107700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-102200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-65100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-20800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-26400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>-11900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-28800</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4476,70 +4724,76 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E102" s="3">
         <v>85300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-80000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>83700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>55700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>54400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>35800</v>
-      </c>
-      <c r="L102" s="3">
-        <v>23600</v>
       </c>
       <c r="M102" s="3">
         <v>23600</v>
       </c>
       <c r="N102" s="3">
-        <v>6700</v>
+        <v>23600</v>
       </c>
       <c r="O102" s="3">
         <v>6700</v>
       </c>
       <c r="P102" s="3">
+        <v>6700</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CVCO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CVCO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>CVCO</t>
   </si>
@@ -656,223 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44653</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44289</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43918</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43554</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42826</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42462</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42091</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41727</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41363</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2244500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2015500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1794800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2142700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1627200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1108100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1061800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>962700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>871200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>773800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>712400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>566700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>533300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>452300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>443100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1681000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1491300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1317700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1545900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1218400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>869100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>831300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>757000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>690600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>615800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>567900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>440500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>413900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>351900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>347100</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>499700</v>
+      </c>
+      <c r="E10" s="3">
         <v>443300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>405200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>533900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>408000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>238200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>229000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>202300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>176300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>158000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>144400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>126100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>119500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>100400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>95900</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -891,8 +903,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -938,9 +951,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,87 +1002,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E14" s="3">
         <v>11100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-5700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-8400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-22000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E15" s="3">
         <v>19300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1082,9 +1104,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1100,104 +1125,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2015900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1815200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1615800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1844300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1425400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1020000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>978400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>882100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>801900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>717000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>666000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>528200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>501800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>431300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>404900</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>228600</v>
+      </c>
+      <c r="E18" s="3">
         <v>200300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>179000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>298400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>201800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>88100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>83400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>80700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>69400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>56800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>46300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>38500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>31500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>21000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>38200</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1216,104 +1248,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1700</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>250500</v>
+      </c>
+      <c r="E21" s="3">
         <v>220800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>196600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>314800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>213800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>92700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>89200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>85400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>73400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>63400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>45700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>36700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>26600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>45000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1321,14 +1360,14 @@
         <v>500</v>
       </c>
       <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
         <v>1600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1341,123 +1380,132 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>4400</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>4400</v>
       </c>
       <c r="N22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O22" s="3">
         <v>4600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7300</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>244700</v>
+      </c>
+      <c r="E23" s="3">
         <v>211100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>199200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>306800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>212000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>96900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>93000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>86700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>78500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>55300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>44000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>37300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>27800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>16600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>32200</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>54100</v>
+      </c>
+      <c r="E24" s="3">
         <v>40000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>41300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>65900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>20300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>17900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>18100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>17300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2500</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1503,105 +1551,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>190600</v>
+      </c>
+      <c r="E26" s="3">
         <v>171000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>157900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>240800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>197700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>76600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>75100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>68600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>61500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>38000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>23800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>29700</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>190600</v>
+      </c>
+      <c r="E27" s="3">
         <v>171000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>157800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>240600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>197700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>76700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>75100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>68600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>61500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>38000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>23800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15200</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1647,9 +1704,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1737,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1695,9 +1755,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1743,9 +1806,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1791,105 +1857,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1700</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>190600</v>
+      </c>
+      <c r="E33" s="3">
         <v>171000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>157800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>240600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>197700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>76600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>75100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>68600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>61500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>38000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>23800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15200</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1935,110 +2010,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>190600</v>
+      </c>
+      <c r="E35" s="3">
         <v>171000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>157800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>240600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>197700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>76600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>75100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>68600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>61500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>38000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>23800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>15200</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44653</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44289</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43918</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43554</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42826</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42462</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42091</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41727</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41363</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2057,8 +2141,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2077,440 +2162,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>236700</v>
+      </c>
+      <c r="E41" s="3">
         <v>356200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>352700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>271400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>244200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>322300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>241800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>187400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>186800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>132500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>97800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>96600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>72900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>47800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>41100</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E42" s="3">
         <v>19800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>20100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>19500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5400</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>108300</v>
+      </c>
+      <c r="E43" s="3">
         <v>105800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>77100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>89300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>96100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>47400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>42800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>40700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>35000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>70300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>54600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>53400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>43600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>42900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>37600</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>295700</v>
+      </c>
+      <c r="E44" s="3">
         <v>252700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>241300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>263200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>244000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>131200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>113500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>116200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>109200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>93900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>94800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>75300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>69700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>68800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>62200</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E45" s="3">
         <v>3000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>48800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>41400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24700</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>824700</v>
+      </c>
+      <c r="E46" s="3">
         <v>910200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>851800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>804600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>744100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>651800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>516200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>462000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>418600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>356800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>298700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>265500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>227800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>194400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>171000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E47" s="3">
         <v>18100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>18600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>34900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>35000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>31600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>32100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>33600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>112800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>118600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>114600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>113900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>120500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>130100</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>263200</v>
+        <v>312500</v>
       </c>
       <c r="E48" s="3">
         <v>263200</v>
       </c>
       <c r="F48" s="3">
+        <v>263200</v>
+      </c>
+      <c r="G48" s="3">
         <v>255000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>181000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>113000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>91100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>63500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>63400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>57000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>55100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>48200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>50100</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>236900</v>
+      </c>
+      <c r="E49" s="3">
         <v>138700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>150200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>144300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>129500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>89500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>90200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>82700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>83000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>80000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>80400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>76700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>78100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>79400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>80900</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2556,9 +2669,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2604,9 +2720,12 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2617,7 +2736,7 @@
         <v>600</v>
       </c>
       <c r="F52" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G52" s="3">
         <v>300</v>
@@ -2629,32 +2748,35 @@
         <v>300</v>
       </c>
       <c r="J52" s="3">
+        <v>300</v>
+      </c>
+      <c r="K52" s="3">
         <v>400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>700</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1100</v>
       </c>
       <c r="N52" s="3">
         <v>1100</v>
       </c>
       <c r="O52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P52" s="3">
         <v>1200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5200</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2700,57 +2822,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1491100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1406600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1354200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1308000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1155000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>951800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>810400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>725200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>674800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>607300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>553800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>502600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>469200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>444500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>437300</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2769,8 +2897,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2789,248 +2918,264 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E57" s="3">
         <v>37200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11700</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E58" s="3">
         <v>6200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7100</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>27200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6600</v>
-      </c>
-      <c r="O58" s="3">
-        <v>10200</v>
       </c>
       <c r="P58" s="3">
         <v>10200</v>
       </c>
       <c r="Q58" s="3">
+        <v>10200</v>
+      </c>
+      <c r="R58" s="3">
         <v>15300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>197600</v>
+      </c>
+      <c r="E59" s="3">
         <v>179800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>160700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>174200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>178300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>153300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>104200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>83300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>72000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>109800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>97900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>77100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>73500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>62700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>58500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>335400</v>
+      </c>
+      <c r="E60" s="3">
         <v>303200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>273300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>293400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>294200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>237100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>172100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>174000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>176300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>140200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>125100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>101500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>99000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>87000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>85500</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E61" s="3">
         <v>38900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>42900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>33800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>54900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>60400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>59900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>72100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>80700</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3058,27 +3203,30 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>21100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>20600</v>
       </c>
       <c r="N62" s="3">
         <v>20600</v>
       </c>
       <c r="O62" s="3">
+        <v>20600</v>
+      </c>
+      <c r="P62" s="3">
         <v>19900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16200</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3124,9 +3272,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3172,9 +3323,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3220,57 +3374,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>388000</v>
+      </c>
+      <c r="E66" s="3">
         <v>342100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>320700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>330500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>323700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>268200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>202800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>195600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>217700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>212900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>200600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>182400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>178800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>267600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>269000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3289,8 +3449,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3336,9 +3497,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3384,9 +3548,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3432,9 +3599,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3480,57 +3650,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1388700</v>
+      </c>
+      <c r="E72" s="3">
         <v>1198200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1027100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>869300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>628800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>431100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>355100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>280100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>209400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>148100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>110200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>81600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>57800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>41600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>36600</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3576,9 +3752,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3624,9 +3803,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3672,57 +3854,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1103200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1064600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1033400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>976300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>830500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>683600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>607600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>529600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>457100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>394400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>353200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>320200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>290400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>176900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>168300</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3768,110 +3956,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44653</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44289</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43918</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43554</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42826</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42462</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42091</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41727</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41363</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>190600</v>
+      </c>
+      <c r="E81" s="3">
         <v>171000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>157800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>240600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>197700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>76600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>75100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>68600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>61500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>38000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>23800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>15200</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3890,56 +4087,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E83" s="3">
         <v>17700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>3700</v>
       </c>
       <c r="L83" s="3">
         <v>3700</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="M83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>3800</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3">
         <v>4000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5600</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3985,9 +4186,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4033,9 +4237,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4081,9 +4288,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4129,9 +4339,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4177,57 +4390,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>267500</v>
+      </c>
+      <c r="E89" s="3">
         <v>178500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>224700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>255700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>144200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>114000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>101700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>32800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>59000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>45800</v>
-      </c>
-      <c r="M89" s="3">
-        <v>25700</v>
       </c>
       <c r="N89" s="3">
         <v>25700</v>
       </c>
       <c r="O89" s="3">
-        <v>20700</v>
+        <v>25700</v>
       </c>
       <c r="P89" s="3">
         <v>20700</v>
       </c>
       <c r="Q89" s="3">
+        <v>20700</v>
+      </c>
+      <c r="R89" s="3">
         <v>16400</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4246,56 +4465,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-44100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-2200</v>
       </c>
       <c r="N91" s="3">
         <v>-2200</v>
       </c>
       <c r="O91" s="3">
-        <v>-800</v>
+        <v>-2200</v>
       </c>
       <c r="P91" s="3">
         <v>-800</v>
       </c>
       <c r="Q91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R91" s="3">
         <v>-70100</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4341,9 +4564,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4389,57 +4615,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-222400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-129300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-159100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7100</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-2100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4458,8 +4690,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4505,9 +4738,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4553,9 +4789,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4601,9 +4840,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4649,57 +4891,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-162800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-147900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-107700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-102200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-65100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-20800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-26400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-28800</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4727,73 +4975,79 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-117700</v>
+      </c>
+      <c r="E102" s="3">
         <v>6600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>85300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>24200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-80000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>83700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>55700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>54400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>35800</v>
-      </c>
-      <c r="M102" s="3">
-        <v>23600</v>
       </c>
       <c r="N102" s="3">
         <v>23600</v>
       </c>
       <c r="O102" s="3">
-        <v>6700</v>
+        <v>23600</v>
       </c>
       <c r="P102" s="3">
         <v>6700</v>
       </c>
       <c r="Q102" s="3">
+        <v>6700</v>
+      </c>
+      <c r="R102" s="3">
         <v>-35400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
